--- a/results/alternatives/P2z_earth_new_zbo_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P2z_earth_new_zbo_MANDATORY_STRESS/results.xlsx
@@ -1563,19 +1563,19 @@
         <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>99.99999999999999</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
         <v>80</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1596,7 +1596,7 @@
         <v>4.944420000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.045</v>
+        <v>0.04500000000000001</v>
       </c>
       <c r="R2" t="n">
         <v>12.32876712328767</v>
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-3.552713678800501e-14</v>
       </c>
     </row>
     <row r="3">
@@ -1673,7 +1673,7 @@
         <v>153.0518</v>
       </c>
       <c r="P3" t="n">
-        <v>6.887331000000001</v>
+        <v>6.887331</v>
       </c>
       <c r="Q3" t="n">
         <v>0.04500000000000001</v>
@@ -1747,13 +1747,13 @@
         <v>30.82224430000005</v>
       </c>
       <c r="N4" t="n">
-        <v>203.1881999999999</v>
+        <v>203.1882</v>
       </c>
       <c r="O4" t="n">
-        <v>203.1881999999999</v>
+        <v>203.1882</v>
       </c>
       <c r="P4" t="n">
-        <v>5.790863699999997</v>
+        <v>5.790863699999999</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0285</v>
@@ -1765,7 +1765,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>26.28542482500007</v>
+        <v>26.28542482500006</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="5">
@@ -1806,19 +1806,19 @@
         <v>287.5</v>
       </c>
       <c r="G5" t="n">
-        <v>195.4999999999999</v>
+        <v>195.5</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>30.82224430000005</v>
@@ -1836,7 +1836,7 @@
         <v>3.141256800000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01200000000000001</v>
+        <v>0.012</v>
       </c>
       <c r="R5" t="n">
         <v>35.44520547945206</v>
@@ -1886,19 +1886,19 @@
         <v>330.5825283000001</v>
       </c>
       <c r="G6" t="n">
-        <v>241.5</v>
+        <v>241.4999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8983220877717394</v>
+        <v>0.8983220877717395</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>37.41747169999991</v>
+        <v>37.41747169999985</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="L6" t="n">
         <v>1.952387500000114</v>
@@ -1907,10 +1907,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>332.6215999999999</v>
+        <v>332.6216</v>
       </c>
       <c r="O6" t="n">
-        <v>332.6215999999999</v>
+        <v>332.6216</v>
       </c>
       <c r="P6" t="n">
         <v>3.9914592</v>
@@ -1963,19 +1963,19 @@
         <v>287.5</v>
       </c>
       <c r="F7" t="n">
-        <v>390.0000572000001</v>
+        <v>390.0000572</v>
       </c>
       <c r="G7" t="n">
         <v>287.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8695653449275365</v>
+        <v>0.8695653449275363</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>58.49994279999987</v>
+        <v>58.49994279999993</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>394.7369</v>
       </c>
       <c r="P7" t="n">
-        <v>4.736842799999999</v>
+        <v>4.7368428</v>
       </c>
       <c r="Q7" t="n">
         <v>0.012</v>
@@ -9449,10 +9449,10 @@
         <v>74.73690000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>74.73690000000002</v>
+        <v>74.73690000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>74.73690000000002</v>
+        <v>74.73690000000001</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -10130,13 +10130,13 @@
         <v>2039</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8983220877717394</v>
+        <v>0.8983220877717395</v>
       </c>
       <c r="J2" t="n">
         <v>0.97</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07167791222826059</v>
+        <v>0.07167791222826048</v>
       </c>
     </row>
     <row r="3">
@@ -10169,13 +10169,13 @@
         <v>2040</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8695653449275365</v>
+        <v>0.8695653449275363</v>
       </c>
       <c r="J3" t="n">
         <v>0.97</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1004346550724635</v>
+        <v>0.1004346550724636</v>
       </c>
     </row>
     <row r="4">
@@ -10535,7 +10535,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0.99</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0.99</v>
@@ -10670,7 +10670,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0.97</v>
@@ -10850,7 +10850,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.8983220877717394</v>
+        <v>0.8983220877717395</v>
       </c>
       <c r="G12" t="n">
         <v>0.97</v>
@@ -10895,7 +10895,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.8695653449275365</v>
+        <v>0.8695653449275363</v>
       </c>
       <c r="G13" t="n">
         <v>0.97</v>
@@ -11969,7 +11969,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0.01200000000000001</v>
+        <v>0.012</v>
       </c>
       <c r="G35" t="n">
         <v>0.02</v>
@@ -22151,7 +22151,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9142.897763133346</v>
+        <v>9142.897763133344</v>
       </c>
     </row>
     <row r="4">
@@ -22251,7 +22251,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>95.91741449999979</v>
+        <v>95.91741449999978</v>
       </c>
     </row>
     <row r="9">
@@ -22271,7 +22271,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="10">
@@ -22311,7 +22311,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.357700076003976</v>
+        <v>6.357700076003974</v>
       </c>
     </row>
     <row r="12">
@@ -22331,7 +22331,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.8695653449275365</v>
+        <v>0.8695653449275363</v>
       </c>
     </row>
     <row r="13">
@@ -22351,7 +22351,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.9999999999999997</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -22451,7 +22451,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>578.8462200000001</v>
+        <v>578.84622</v>
       </c>
     </row>
     <row r="19">

--- a/results/alternatives/P2z_earth_new_zbo_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P2z_earth_new_zbo_MANDATORY_STRESS/results.xlsx
@@ -423,13 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TerraPlan export</t>
+          <t>Выгрузка TerraPlan, версия</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>plan_id</t>
+          <t>план (plan_id)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>scenario_id</t>
+          <t>сценарий (scenario_id)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -465,96 +465,240 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feasible</t>
+          <t>план исполним</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>unit:fuel</t>
+          <t>жёстких нарушений / отклонений от ориентиров / предупреждений</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>3 / 2 / 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>unit:money</t>
+          <t>единица: fuel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mln conventional units, constant 2035 prices</t>
+          <t>т</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>unit:capacity</t>
+          <t>единица: money</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t/year</t>
+          <t>млн у.е., постоянные цены 2035 г.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>unit:reservation_rate</t>
+          <t>единица: capacity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mln per (t/year)</t>
+          <t>т/год</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>unit:service_level</t>
+          <t>единица: reservation_rate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>share 0..1</t>
+          <t>млн у.е. за (т/год)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>unit:time_step</t>
+          <t>единица: service_level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>calendar month</t>
+          <t>доля 0..1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sheets</t>
+          <t>единица: time_step</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>календарный месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>периоды</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2035-01 … 2040-12, шаг — календарный месяц; подготовительный период до 2035-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>листы</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>yearly_balance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>годовой баланс: спрос, выдача, дефицит, уровни сервиса, поступление, потери, запасы, 45-дневный резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>inventory_trace</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>помесячный материальный баланс и стоимость хранения</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>source_schedule</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>по источникам и годам: резерв, заказ, план/факт поставки, цена, оплачиваемый объём (take-or-pay), платежи</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>financial_breakdown</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>по годам: закупка, резервирование, хранение, постоянный OPEX, CAPEX, итого, PV, накопленный CAPEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>constraint_checks</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>нарушения: правило, строгость, год, месяц, источник, факт, лимит, превышение, сообщение</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>constraint_matrix</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>матрица проверок: каждое правило × год, включая выполненные</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>delivery_schedule</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>календарь поставок: месяц поставки, месяц размещения заказа, срок поставки, допустимость</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>kpi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>итоговые показатели</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>investments</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>инвестиционные решения: даты опциона, реализации, ввода</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>assumptions</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>реестр допущений TEAM_ASSUMPTION: значение, единица, статус, диапазон, обоснование</t>
         </is>
       </c>
     </row>
@@ -778,7 +922,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>share per year (real)</t>
+          <t>доля в год (реальная ставка)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -793,7 +937,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Real discount rate for long-lived infrastructure with technology risk. Not given by the organizer. Used identically for all alternatives; sensitivity 0–12 % in experiments/run_sensitivity.py.
+          <t xml:space="preserve">Реальная ставка дисконтирования для долгоживущей инфраструктуры с технологическим риском. Организатором не задана. Применяется одинаково ко всем альтернативам; чувствительность 0–12 % в experiments/run_sensitivity.py.
 </t>
         </is>
       </c>
@@ -811,7 +955,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>год</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -826,7 +970,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year; PV factor = 1/(1+r)^(year-2035).</t>
+          <t>Годовые денежные потоки датируются началом каждого года; коэффициент приведения = 1/(1+r)^(год − 2035).</t>
         </is>
       </c>
     </row>
@@ -843,7 +987,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>enum start|mid|end</t>
+          <t>перечисление start|mid|end</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -858,7 +1002,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year (exponent year-2035); mid/end-year conventions available and applied identically to all alternatives.</t>
+          <t>Момент внутри года, к которому отнесён годовой поток — начало (показатель степени год − 2035), середина (+0,5) или конец (+1); одинаково для всех альтернатив.</t>
         </is>
       </c>
     </row>
@@ -875,7 +1019,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -890,7 +1034,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Earliest order date of the preparatory period (Earth-Core needs 12 months before 2035-01).</t>
+          <t>Самая ранняя дата заказа в подготовительном периоде (Earth-Core требует 12 месяцев до 2035-01).</t>
         </is>
       </c>
     </row>
@@ -907,7 +1051,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>enum min|max|mean</t>
+          <t>перечисление min|max|mean</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -922,7 +1066,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Conservative end of the organizer lead-time ranges (Earth-New 24 months, ISRU 2 months).</t>
+          <t>Консервативный край диапазонов сроков поставки организатора (Earth-New 24 месяца, ISRU 2 месяца).</t>
         </is>
       </c>
     </row>
@@ -939,7 +1083,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>weeks</t>
+          <t>недель</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -954,7 +1098,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>365/12/7. Week lead times converted with ceil(weeks/4.345) -&gt; Emergency 6 weeks = 2 months.</t>
+          <t>365/12/7. Сроки в неделях переводятся как ceil(недели/4,345) -&gt; Emergency 6 недель = 2 месяца.</t>
         </is>
       </c>
     </row>
@@ -971,7 +1115,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>дней</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -986,7 +1130,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>365/12; day-denominated lead times converted with ceil.</t>
+          <t>365/12; сроки в днях переводятся с округлением вверх.</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1147,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1018,7 +1162,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Case gives no ZBO build time; modernization active from the CAPEX month. Varied in sensitivity.</t>
+          <t>Кейс не задаёт срок модернизации ZBO; она считается действующей с месяца оплаты CAPEX. Варьируется в анализе чувствительности.</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1179,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1050,7 +1194,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The 18–24 month Earth-New lead time is read as decision-to-first-delivery; orders are placed during preparation.</t>
+          <t>Срок Earth-New 18–24 месяца трактуется как время от решения до первой поставки; заказы размещаются в период подготовки, после ввода дополнительный срок заказа 0 месяцев.</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1211,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1082,7 +1226,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunar-ISRU available from 2038 once CAPEX is financed before 2038.</t>
+          <t>Lunar-ISRU доступен с 2038 года при финансировании CAPEX до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1243,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1114,7 +1258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CAPEX 1250 must be financed before 2038.</t>
+          <t>CAPEX 1 250 млн должен быть профинансирован до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1275,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>map source_id -&gt; investment_id</t>
+          <t>отображение source_id -&gt; investment_id</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1146,7 +1290,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Earth-New capacity requires the exercised option; Lunar-ISRU requires the pilot CAPEX.</t>
+          <t>Мощность Earth-New требует реализованного опциона; Lunar-ISRU — CAPEX пилотного производства.</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1307,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>map investment_id -&gt; storage_id</t>
+          <t>отображение investment_id -&gt; storage_id</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1178,7 +1322,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ZBO modernization switches the active storage mode (capacity 120 t, losses 1.2 %, OPEX 12/yr).</t>
+          <t>Модернизация ZBO переключает активный режим хранилища (ёмкость 120 т, потери 1,2 %, OPEX 12 млн/год).</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1339,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>share of annual total demand</t>
+          <t>доля годового общего спроса</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1210,7 +1354,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emergency counts as the base channel in a year when its ordered volume exceeds 20 % of that year's demand.</t>
+          <t>Emergency считается базовым каналом в году, когда заказанный у него объём превышает 20 % спроса этого года.</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1371,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1242,7 +1386,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Average physical stock per month = (I_start + I_end)/2; holding = 0.72 x average x 1/12.</t>
+          <t>Средний физический запас за месяц = (I_start + I_end)/2; стоимость хранения = 0,72 × средний запас × 1/12.</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1403,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1274,7 +1418,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hard violation when end-of-month stock &gt; capacity; warning when stock after inflow (before withdrawals) &gt; capacity.</t>
+          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1435,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1306,7 +1450,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contracted Emergency reserve counts only if stock covers demand during the 6-week lead time and reserved Emergency capacity &gt;= R_y.</t>
+          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1467,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1338,7 +1482,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>The preparatory-period purchase pays the source reservation rate on the purchased tonnage for one year; booked in 2035.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1499,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1370,7 +1514,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Holding cost charged from 2035-01; storage time in the preparatory period (&lt; 1 month) is not charged.</t>
+          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1531,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1402,7 +1546,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Organizer convention — uniform demand within the year, 365 days.</t>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10267,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2039: total service level 0.8983 &lt; 0.97 (shortage 37.417 t) [guideline in this scenario]</t>
+          <t>2039: общий уровень сервиса 0.8983 &lt; 0.97 (дефицит 37.417 т) [в этом сценарии — ориентир, не жёсткое ограничение]</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -10162,7 +10306,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2040: total service level 0.8696 &lt; 0.97 (shortage 58.500 t) [guideline in this scenario]</t>
+          <t>2040: общий уровень сервиса 0.8696 &lt; 0.97 (дефицит 58.500 т) [в этом сценарии — ориентир, не жёсткое ограничение]</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -10201,7 +10345,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2038-01: physical stock 30.822 t &lt; 45-day reserve 35.445 t</t>
+          <t>2038-01: физический запас 30.822 т &lt; 45-дневного резерва 35.445 т</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -10243,7 +10387,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2039-01: physical stock 1.952 t &lt; 45-day reserve 45.370 t</t>
+          <t>2039-01: физический запас 1.952 т &lt; 45-дневного резерва 45.370 т</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -10285,7 +10429,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2040-01: physical stock 0.000 t &lt; 45-day reserve 55.295 t</t>
+          <t>2040-01: физический запас 0.000 т &lt; 45-дневного резерва 55.295 т</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -11682,7 +11826,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11695,7 +11839,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11875,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11744,7 +11888,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11780,7 +11924,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -11793,7 +11937,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11829,7 +11973,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -11842,7 +11986,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11878,7 +12022,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -11891,7 +12035,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11927,7 +12071,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -11940,7 +12084,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12819,7 +12963,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -12829,7 +12973,7 @@
         <v/>
       </c>
       <c r="I53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -13152,7 +13296,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
@@ -13162,7 +13306,7 @@
         <v/>
       </c>
       <c r="I60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -14088,7 +14232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:N145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14157,6 +14301,11 @@
           <t>lead_time_ok</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>lead_time_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14212,6 +14361,11 @@
       <c r="M2" t="b">
         <v>1</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14267,6 +14421,11 @@
       <c r="M3" t="b">
         <v>1</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14322,6 +14481,11 @@
       <c r="M4" t="b">
         <v>1</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14377,6 +14541,11 @@
       <c r="M5" t="b">
         <v>1</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14432,6 +14601,11 @@
       <c r="M6" t="b">
         <v>1</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14487,6 +14661,11 @@
       <c r="M7" t="b">
         <v>1</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14542,6 +14721,11 @@
       <c r="M8" t="b">
         <v>1</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14597,6 +14781,11 @@
       <c r="M9" t="b">
         <v>1</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14652,6 +14841,11 @@
       <c r="M10" t="b">
         <v>1</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14707,6 +14901,11 @@
       <c r="M11" t="b">
         <v>1</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14762,6 +14961,11 @@
       <c r="M12" t="b">
         <v>1</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14817,6 +15021,11 @@
       <c r="M13" t="b">
         <v>1</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14872,6 +15081,11 @@
       <c r="M14" t="b">
         <v>1</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14927,6 +15141,11 @@
       <c r="M15" t="b">
         <v>1</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14982,6 +15201,11 @@
       <c r="M16" t="b">
         <v>1</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15037,6 +15261,11 @@
       <c r="M17" t="b">
         <v>1</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -15092,6 +15321,11 @@
       <c r="M18" t="b">
         <v>1</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15147,6 +15381,11 @@
       <c r="M19" t="b">
         <v>1</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -15202,6 +15441,11 @@
       <c r="M20" t="b">
         <v>1</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -15257,6 +15501,11 @@
       <c r="M21" t="b">
         <v>1</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -15312,6 +15561,11 @@
       <c r="M22" t="b">
         <v>1</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -15367,6 +15621,11 @@
       <c r="M23" t="b">
         <v>1</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -15422,6 +15681,11 @@
       <c r="M24" t="b">
         <v>1</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15477,6 +15741,11 @@
       <c r="M25" t="b">
         <v>1</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -15532,6 +15801,11 @@
       <c r="M26" t="b">
         <v>1</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15572,11 +15846,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2035-01</t>
+          <t>2037-01</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -15585,7 +15859,12 @@
         </is>
       </c>
       <c r="M27" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -15642,6 +15921,11 @@
       <c r="M28" t="b">
         <v>1</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15682,11 +15966,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J29" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2035-02</t>
+          <t>2037-02</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -15695,7 +15979,12 @@
         </is>
       </c>
       <c r="M29" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -15752,6 +16041,11 @@
       <c r="M30" t="b">
         <v>1</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15792,11 +16086,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2035-03</t>
+          <t>2037-03</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -15805,7 +16099,12 @@
         </is>
       </c>
       <c r="M31" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -15862,6 +16161,11 @@
       <c r="M32" t="b">
         <v>1</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15902,11 +16206,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J33" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2035-04</t>
+          <t>2037-04</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -15915,7 +16219,12 @@
         </is>
       </c>
       <c r="M33" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -15972,6 +16281,11 @@
       <c r="M34" t="b">
         <v>1</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16012,11 +16326,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2035-05</t>
+          <t>2037-05</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -16025,7 +16339,12 @@
         </is>
       </c>
       <c r="M35" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -16082,6 +16401,11 @@
       <c r="M36" t="b">
         <v>1</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -16122,11 +16446,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2035-06</t>
+          <t>2037-06</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -16135,7 +16459,12 @@
         </is>
       </c>
       <c r="M37" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -16192,6 +16521,11 @@
       <c r="M38" t="b">
         <v>1</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -16232,11 +16566,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J39" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2035-07</t>
+          <t>2037-07</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -16245,7 +16579,12 @@
         </is>
       </c>
       <c r="M39" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -16302,6 +16641,11 @@
       <c r="M40" t="b">
         <v>1</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -16342,11 +16686,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2035-08</t>
+          <t>2037-08</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -16355,7 +16699,12 @@
         </is>
       </c>
       <c r="M41" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -16412,6 +16761,11 @@
       <c r="M42" t="b">
         <v>1</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -16452,11 +16806,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J43" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2035-09</t>
+          <t>2037-09</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -16465,7 +16819,12 @@
         </is>
       </c>
       <c r="M43" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -16522,6 +16881,11 @@
       <c r="M44" t="b">
         <v>1</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -16562,11 +16926,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J45" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2035-10</t>
+          <t>2037-10</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -16575,7 +16939,12 @@
         </is>
       </c>
       <c r="M45" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -16632,6 +17001,11 @@
       <c r="M46" t="b">
         <v>1</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16672,11 +17046,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J47" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2035-11</t>
+          <t>2037-11</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -16685,7 +17059,12 @@
         </is>
       </c>
       <c r="M47" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -16742,6 +17121,11 @@
       <c r="M48" t="b">
         <v>1</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -16782,11 +17166,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2035-12</t>
+          <t>2037-12</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -16795,7 +17179,12 @@
         </is>
       </c>
       <c r="M49" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -16852,6 +17241,11 @@
       <c r="M50" t="b">
         <v>1</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -16892,11 +17286,11 @@
         <v>5.98095</v>
       </c>
       <c r="J51" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2036-01</t>
+          <t>2038-01</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -16905,7 +17299,12 @@
         </is>
       </c>
       <c r="M51" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -16962,6 +17361,11 @@
       <c r="M52" t="b">
         <v>1</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17002,11 +17406,11 @@
         <v>5.98095</v>
       </c>
       <c r="J53" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2036-02</t>
+          <t>2038-02</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -17015,7 +17419,12 @@
         </is>
       </c>
       <c r="M53" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -17072,6 +17481,11 @@
       <c r="M54" t="b">
         <v>1</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -17112,11 +17526,11 @@
         <v>5.98095</v>
       </c>
       <c r="J55" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2036-03</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -17125,7 +17539,12 @@
         </is>
       </c>
       <c r="M55" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -17182,6 +17601,11 @@
       <c r="M56" t="b">
         <v>1</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17222,11 +17646,11 @@
         <v>5.98095</v>
       </c>
       <c r="J57" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2036-04</t>
+          <t>2038-04</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -17235,7 +17659,12 @@
         </is>
       </c>
       <c r="M57" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -17292,6 +17721,11 @@
       <c r="M58" t="b">
         <v>1</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -17332,11 +17766,11 @@
         <v>5.98095</v>
       </c>
       <c r="J59" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2036-05</t>
+          <t>2038-05</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -17345,7 +17779,12 @@
         </is>
       </c>
       <c r="M59" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -17402,6 +17841,11 @@
       <c r="M60" t="b">
         <v>1</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17442,11 +17886,11 @@
         <v>5.98095</v>
       </c>
       <c r="J61" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2036-06</t>
+          <t>2038-06</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -17455,7 +17899,12 @@
         </is>
       </c>
       <c r="M61" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -17512,6 +17961,11 @@
       <c r="M62" t="b">
         <v>1</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -17552,11 +18006,11 @@
         <v>5.98095</v>
       </c>
       <c r="J63" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2036-07</t>
+          <t>2038-07</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -17565,7 +18019,12 @@
         </is>
       </c>
       <c r="M63" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -17622,6 +18081,11 @@
       <c r="M64" t="b">
         <v>1</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17662,11 +18126,11 @@
         <v>5.98095</v>
       </c>
       <c r="J65" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2036-08</t>
+          <t>2038-08</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -17675,7 +18139,12 @@
         </is>
       </c>
       <c r="M65" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -17732,6 +18201,11 @@
       <c r="M66" t="b">
         <v>1</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -17772,11 +18246,11 @@
         <v>5.98095</v>
       </c>
       <c r="J67" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2036-09</t>
+          <t>2038-09</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -17785,7 +18259,12 @@
         </is>
       </c>
       <c r="M67" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -17842,6 +18321,11 @@
       <c r="M68" t="b">
         <v>1</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -17882,11 +18366,11 @@
         <v>5.98095</v>
       </c>
       <c r="J69" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2036-10</t>
+          <t>2038-10</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -17895,7 +18379,12 @@
         </is>
       </c>
       <c r="M69" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -17952,6 +18441,11 @@
       <c r="M70" t="b">
         <v>1</v>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -17992,11 +18486,11 @@
         <v>5.98095</v>
       </c>
       <c r="J71" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2036-11</t>
+          <t>2038-11</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -18005,7 +18499,12 @@
         </is>
       </c>
       <c r="M71" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -18062,6 +18561,11 @@
       <c r="M72" t="b">
         <v>1</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -18102,11 +18606,11 @@
         <v>5.98095</v>
       </c>
       <c r="J73" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2036-12</t>
+          <t>2038-12</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -18115,7 +18619,12 @@
         </is>
       </c>
       <c r="M73" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -18172,6 +18681,11 @@
       <c r="M74" t="b">
         <v>1</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -18227,6 +18741,11 @@
       <c r="M75" t="b">
         <v>1</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -18267,20 +18786,25 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J76" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
+          <t>2039-01</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
           <t>2037-01</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>2037-01</t>
-        </is>
-      </c>
       <c r="M76" t="b">
         <v>1</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -18337,6 +18861,11 @@
       <c r="M77" t="b">
         <v>1</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18392,6 +18921,11 @@
       <c r="M78" t="b">
         <v>1</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -18432,11 +18966,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J79" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2037-02</t>
+          <t>2039-02</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -18446,6 +18980,11 @@
       </c>
       <c r="M79" t="b">
         <v>1</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -18502,6 +19041,11 @@
       <c r="M80" t="b">
         <v>1</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -18557,6 +19101,11 @@
       <c r="M81" t="b">
         <v>1</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -18597,11 +19146,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J82" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2037-03</t>
+          <t>2039-03</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -18611,6 +19160,11 @@
       </c>
       <c r="M82" t="b">
         <v>1</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -18667,6 +19221,11 @@
       <c r="M83" t="b">
         <v>1</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -18722,6 +19281,11 @@
       <c r="M84" t="b">
         <v>1</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -18762,11 +19326,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J85" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2037-04</t>
+          <t>2039-04</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -18776,6 +19340,11 @@
       </c>
       <c r="M85" t="b">
         <v>1</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -18832,6 +19401,11 @@
       <c r="M86" t="b">
         <v>1</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -18887,6 +19461,11 @@
       <c r="M87" t="b">
         <v>1</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -18927,11 +19506,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J88" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2037-05</t>
+          <t>2039-05</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -18941,6 +19520,11 @@
       </c>
       <c r="M88" t="b">
         <v>1</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -18997,6 +19581,11 @@
       <c r="M89" t="b">
         <v>1</v>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -19052,6 +19641,11 @@
       <c r="M90" t="b">
         <v>1</v>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -19092,11 +19686,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J91" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2037-06</t>
+          <t>2039-06</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -19106,6 +19700,11 @@
       </c>
       <c r="M91" t="b">
         <v>1</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -19162,6 +19761,11 @@
       <c r="M92" t="b">
         <v>1</v>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -19217,6 +19821,11 @@
       <c r="M93" t="b">
         <v>1</v>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -19257,11 +19866,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J94" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2037-07</t>
+          <t>2039-07</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -19271,6 +19880,11 @@
       </c>
       <c r="M94" t="b">
         <v>1</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -19327,6 +19941,11 @@
       <c r="M95" t="b">
         <v>1</v>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -19382,6 +20001,11 @@
       <c r="M96" t="b">
         <v>1</v>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -19422,11 +20046,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J97" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2037-08</t>
+          <t>2039-08</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -19436,6 +20060,11 @@
       </c>
       <c r="M97" t="b">
         <v>1</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -19492,6 +20121,11 @@
       <c r="M98" t="b">
         <v>1</v>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -19547,6 +20181,11 @@
       <c r="M99" t="b">
         <v>1</v>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -19587,11 +20226,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J100" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2037-09</t>
+          <t>2039-09</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -19601,6 +20240,11 @@
       </c>
       <c r="M100" t="b">
         <v>1</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -19657,6 +20301,11 @@
       <c r="M101" t="b">
         <v>1</v>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -19712,6 +20361,11 @@
       <c r="M102" t="b">
         <v>1</v>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -19752,11 +20406,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J103" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2037-10</t>
+          <t>2039-10</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -19766,6 +20420,11 @@
       </c>
       <c r="M103" t="b">
         <v>1</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -19822,6 +20481,11 @@
       <c r="M104" t="b">
         <v>1</v>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -19877,6 +20541,11 @@
       <c r="M105" t="b">
         <v>1</v>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -19917,11 +20586,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J106" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2037-11</t>
+          <t>2039-11</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -19931,6 +20600,11 @@
       </c>
       <c r="M106" t="b">
         <v>1</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -19987,6 +20661,11 @@
       <c r="M107" t="b">
         <v>1</v>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -20042,6 +20721,11 @@
       <c r="M108" t="b">
         <v>1</v>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -20082,11 +20766,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J109" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2037-12</t>
+          <t>2039-12</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -20096,6 +20780,11 @@
       </c>
       <c r="M109" t="b">
         <v>1</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -20152,6 +20841,11 @@
       <c r="M110" t="b">
         <v>1</v>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -20207,6 +20901,11 @@
       <c r="M111" t="b">
         <v>1</v>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -20247,11 +20946,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J112" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2038-01</t>
+          <t>2040-01</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -20261,6 +20960,11 @@
       </c>
       <c r="M112" t="b">
         <v>1</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -20317,6 +21021,11 @@
       <c r="M113" t="b">
         <v>1</v>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -20372,6 +21081,11 @@
       <c r="M114" t="b">
         <v>1</v>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -20412,11 +21126,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J115" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2038-02</t>
+          <t>2040-02</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -20426,6 +21140,11 @@
       </c>
       <c r="M115" t="b">
         <v>1</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -20482,6 +21201,11 @@
       <c r="M116" t="b">
         <v>1</v>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -20537,6 +21261,11 @@
       <c r="M117" t="b">
         <v>1</v>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -20577,11 +21306,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J118" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2038-03</t>
+          <t>2040-03</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -20591,6 +21320,11 @@
       </c>
       <c r="M118" t="b">
         <v>1</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -20647,6 +21381,11 @@
       <c r="M119" t="b">
         <v>1</v>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -20702,6 +21441,11 @@
       <c r="M120" t="b">
         <v>1</v>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -20742,11 +21486,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J121" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2038-04</t>
+          <t>2040-04</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -20756,6 +21500,11 @@
       </c>
       <c r="M121" t="b">
         <v>1</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -20812,6 +21561,11 @@
       <c r="M122" t="b">
         <v>1</v>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -20867,6 +21621,11 @@
       <c r="M123" t="b">
         <v>1</v>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -20907,11 +21666,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J124" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2038-05</t>
+          <t>2040-05</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -20921,6 +21680,11 @@
       </c>
       <c r="M124" t="b">
         <v>1</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -20977,6 +21741,11 @@
       <c r="M125" t="b">
         <v>1</v>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -21032,6 +21801,11 @@
       <c r="M126" t="b">
         <v>1</v>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -21072,11 +21846,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J127" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2038-06</t>
+          <t>2040-06</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -21086,6 +21860,11 @@
       </c>
       <c r="M127" t="b">
         <v>1</v>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -21142,6 +21921,11 @@
       <c r="M128" t="b">
         <v>1</v>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -21197,6 +21981,11 @@
       <c r="M129" t="b">
         <v>1</v>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -21237,11 +22026,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J130" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2038-07</t>
+          <t>2040-07</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -21251,6 +22040,11 @@
       </c>
       <c r="M130" t="b">
         <v>1</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -21307,6 +22101,11 @@
       <c r="M131" t="b">
         <v>1</v>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -21362,6 +22161,11 @@
       <c r="M132" t="b">
         <v>1</v>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -21402,11 +22206,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J133" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2038-08</t>
+          <t>2040-08</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -21416,6 +22220,11 @@
       </c>
       <c r="M133" t="b">
         <v>1</v>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -21472,6 +22281,11 @@
       <c r="M134" t="b">
         <v>1</v>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -21527,6 +22341,11 @@
       <c r="M135" t="b">
         <v>1</v>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -21567,11 +22386,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J136" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2038-09</t>
+          <t>2040-09</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -21581,6 +22400,11 @@
       </c>
       <c r="M136" t="b">
         <v>1</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -21637,6 +22461,11 @@
       <c r="M137" t="b">
         <v>1</v>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -21692,6 +22521,11 @@
       <c r="M138" t="b">
         <v>1</v>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -21732,11 +22566,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J139" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2038-10</t>
+          <t>2040-10</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -21746,6 +22580,11 @@
       </c>
       <c r="M139" t="b">
         <v>1</v>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -21802,6 +22641,11 @@
       <c r="M140" t="b">
         <v>1</v>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -21857,6 +22701,11 @@
       <c r="M141" t="b">
         <v>1</v>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -21897,11 +22746,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J142" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2038-11</t>
+          <t>2040-11</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -21911,6 +22760,11 @@
       </c>
       <c r="M142" t="b">
         <v>1</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -21967,6 +22821,11 @@
       <c r="M143" t="b">
         <v>1</v>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -22022,6 +22881,11 @@
       <c r="M144" t="b">
         <v>1</v>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -22062,11 +22926,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J145" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2038-12</t>
+          <t>2040-12</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -22076,6 +22940,11 @@
       </c>
       <c r="M145" t="b">
         <v>1</v>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -22671,7 +23540,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/results/alternatives/P2z_earth_new_zbo_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P2z_earth_new_zbo_MANDATORY_STRESS/results.xlsx
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1547,6 +1547,39 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>undelivered_volume_paid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>логическое</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[true, false]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
         </is>
       </c>
     </row>
@@ -11815,18 +11848,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11839,7 +11872,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11864,18 +11897,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11888,7 +11921,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11913,18 +11946,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -11937,7 +11970,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11962,18 +11995,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -11986,7 +12019,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12011,18 +12044,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -12035,7 +12068,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12060,18 +12093,18 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -12084,7 +12117,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12244,7 +12277,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -12268,7 +12301,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2035-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12479,7 +12512,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -12503,7 +12536,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12714,11 +12747,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>30.82224430000005</v>
+        <v>25.44727350000007</v>
       </c>
       <c r="G48" t="n">
         <v>70</v>
@@ -12738,7 +12771,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13047,7 +13080,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -13071,7 +13104,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2038-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13380,7 +13413,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -13404,7 +13437,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2039-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13844,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -13835,7 +13868,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2040-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>

--- a/results/alternatives/P2z_earth_new_zbo_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P2z_earth_new_zbo_MANDATORY_STRESS/results.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1579,6 +1579,105 @@
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exp10_demand_max</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>дополнительный относительный рост спроса</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exp10_isru_reduction_max</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exp10_price_half_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>относительное отклонение переменной цены от обязательного стресса</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[-0.1, 0.1]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
         </is>
       </c>

--- a/results/alternatives/P2z_earth_new_zbo_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P2z_earth_new_zbo_MANDATORY_STRESS/results.xlsx
@@ -7542,7 +7542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7651,6 +7651,11 @@
           <t>reservation_payment_mln</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7726,6 +7731,9 @@
       <c r="U2" t="n">
         <v>1.93647</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7801,6 +7809,9 @@
       <c r="U3" t="n">
         <v>49.4442</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7876,6 +7887,9 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7951,6 +7965,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8026,6 +8043,9 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8101,6 +8121,9 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8176,6 +8199,9 @@
       <c r="U8" t="n">
         <v>68.8734</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8251,6 +8277,9 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8326,6 +8355,9 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8401,6 +8433,9 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8476,6 +8511,9 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8551,6 +8589,9 @@
       <c r="U13" t="n">
         <v>85.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8626,6 +8667,9 @@
       <c r="U14" t="n">
         <v>0</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8701,6 +8745,9 @@
       <c r="U15" t="n">
         <v>3.9567</v>
       </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8776,6 +8823,9 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8851,6 +8901,9 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8926,6 +8979,9 @@
       <c r="U18" t="n">
         <v>85.5</v>
       </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9001,6 +9057,9 @@
       <c r="U19" t="n">
         <v>0</v>
       </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9076,6 +9135,9 @@
       <c r="U20" t="n">
         <v>21.5316</v>
       </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9151,6 +9213,9 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9226,6 +9291,9 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9301,6 +9369,9 @@
       <c r="U23" t="n">
         <v>85.5</v>
       </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9376,6 +9447,9 @@
       <c r="U24" t="n">
         <v>1.8933</v>
       </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9451,6 +9525,9 @@
       <c r="U25" t="n">
         <v>39</v>
       </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9526,6 +9603,9 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9601,6 +9681,9 @@
       <c r="U27" t="n">
         <v>0</v>
       </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9676,6 +9759,9 @@
       <c r="U28" t="n">
         <v>85.5</v>
       </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9751,6 +9837,9 @@
       <c r="U29" t="n">
         <v>11.21055</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9826,6 +9915,9 @@
       <c r="U30" t="n">
         <v>39</v>
       </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9901,6 +9993,9 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9974,6 +10069,9 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9988,7 +10086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10052,6 +10150,11 @@
           <t>cumulative_capex_mln</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10094,6 +10197,9 @@
       <c r="L2" t="n">
         <v>360</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10136,6 +10242,9 @@
       <c r="L3" t="n">
         <v>360</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10178,6 +10287,9 @@
       <c r="L4" t="n">
         <v>540</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10220,6 +10332,9 @@
       <c r="L5" t="n">
         <v>540</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10262,6 +10377,9 @@
       <c r="L6" t="n">
         <v>540</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10303,6 +10421,9 @@
       </c>
       <c r="L7" t="n">
         <v>540</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23090,7 +23211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23528,11 +23649,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>opening_inventory_t</t>
+          <t>take_or_pay_topup_mln</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.328859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -23548,11 +23669,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>closing_inventory_t</t>
+          <t>opening_inventory_t</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>12.328859</v>
       </c>
     </row>
     <row r="24">
@@ -23568,11 +23689,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>closing_inventory_t</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -23588,11 +23709,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -23608,11 +23729,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>guideline_violations</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -23628,10 +23749,10 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23648,11 +23769,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>checks_total</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>78</v>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -23668,10 +23789,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>73</v>
       </c>
     </row>

--- a/results/alternatives/P2z_earth_new_zbo_MANDATORY_STRESS/results.xlsx
+++ b/results/alternatives/P2z_earth_new_zbo_MANDATORY_STRESS/results.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="preparatory_period" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="contract_reserve_proof" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions, preparatory_period, contract_reserve_proof</t>
         </is>
       </c>
     </row>
@@ -874,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1398,7 +1400,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"end_of_month_hard_peak_warning"</t>
+          <t>"end_of_month_and_intra_month_peak_hard"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1418,24 +1420,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
+          <t>Оба превышения ёмкости — жёсткие нарушения. Проверяется запас на конец месяца и расчётный пик внутри месяца при заявленном дроблении поставок (intra_month_delivery_batches): физическая исполнимость плана доказывается графиком поступлений, а не пометкой допущения.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_reserve_equivalence</t>
+          <t>intra_month_delivery_batches</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"stock_covers_lead_time_and_reserved_capacity_covers_45d"</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>правило</t>
+          <t>партий в месяц</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1445,29 +1447,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>[1, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
+          <t>Месячный объём канала приходит N равными партиями, равномерно распределёнными по месяцу, при равномерной выдаче потребителям (конвенция организатора). Пик запаса после партии j равен I_нач + (j·нетто − (j−1)·выдача)/N, максимум берётся по j = 1..N. При N = 1 это запас сразу после единственного поступления, до выдачи, — консервативный край без допущения о внутримесячной синхронизации поставок и выдачи. При N → ∞ пик стремится к max(запас на начало, запас на конец). Выбрано N = 1: организатор не задаёт размер отдельной партии, и ни один принятый план команды не нуждается в дроблении. Чувствительность к N = 2 и N = 4 показана в results/intra_month/intra_month_capacity.md.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opening_stock_reservation_years</t>
+          <t>emergency_reserve_equivalence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>"contracted_batch_schedule_and_waiting_cover"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>лет</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1477,29 +1479,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
+          <t>Договорный аварийный резерв засчитывается только при одновременном выполнении пяти условий, каждое из которых печатается отдельной строкой в contract_reserve_proof: (1) канал доступен в этом году; (2) договорный срок исполнения партии не быстрее срока поставки канала по данным организатора; (3) нетто-объём гарантированной партии после потерь хранилища &gt;= R_y; (4) зарезервированная мощность канала за вычетом обычных заказов года &gt;= партия × число активаций; (5) физический запас на начало года покрывает спрос за время активации плюс срок исполнения. Сам по себе лимит мощности канала (80 т/год) эквивалентности не доказывает. Если блок inventory_policy.emergency_contract не задан, эквивалентность не доказана и действует физический резерв. Правило следует кейсу, §«Начальный запас и резерв».</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prep_period_holding_charged</t>
+          <t>opening_stock_reservation_years</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>логическое</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1509,176 +1511,319 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[true, false]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>intra_year_demand_profile</t>
+          <t>prep_period_holding_charged</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"uniform"</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>перечисление</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CASE_INPUT</t>
+          <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>["uniform"]</t>
+          <t>[true, false]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+          <t>Хранение начального запаса начисляется с фактического месяца поставки, а не с 2035-01: ранняя поставка начального запаса не хранится бесплатно. Правило то же, что и в основном периоде (трапеция): в месяц поставки средний запас равен половине поступления, в каждый последующий месяц подготовительного периода — полному нетто-запасу. Расход относится на первый финансовый год (2035), как закупка и плата за резерв подготовительного периода. Значение false выключает начисление и оставлено только для сопоставления с прежней версией расчёта.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>intra_year_demand_profile</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"uniform"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>перечисление</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>["uniform"]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>undelivered_volume_paid</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>логическое</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CASE_INPUT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>[true, false]</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
 </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>exp10_demand_max</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>дополнительный относительный рост спроса</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
 </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>exp10_isru_reduction_max</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
 </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>exp10_price_half_range</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>относительное отклонение переменной цены от обязательного стресса</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>[-0.1, 0.1]</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>opening_t</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrived_t</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>closing_t</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>holding_cost_mln</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.36986577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>(empty)</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2415,6 +2560,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>peak_stock_t</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>delivery_batches</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>inflow_A_t</t>
         </is>
       </c>
@@ -2487,6 +2642,12 @@
         <v>0.7520604900000002</v>
       </c>
       <c r="U2" t="n">
+        <v>21.07315733333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2558,6 +2719,12 @@
         <v>0.7767183900000002</v>
       </c>
       <c r="U3" t="n">
+        <v>21.48412233333334</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2629,6 +2796,12 @@
         <v>0.8013762900000003</v>
       </c>
       <c r="U4" t="n">
+        <v>21.89508733333334</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2700,6 +2873,12 @@
         <v>0.8260341900000004</v>
       </c>
       <c r="U5" t="n">
+        <v>22.30605233333334</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2771,6 +2950,12 @@
         <v>0.8506920900000003</v>
       </c>
       <c r="U6" t="n">
+        <v>22.71701733333334</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2842,6 +3027,12 @@
         <v>0.8753499900000005</v>
       </c>
       <c r="U7" t="n">
+        <v>23.12798233333334</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2913,6 +3104,12 @@
         <v>0.9000078900000005</v>
       </c>
       <c r="U8" t="n">
+        <v>23.53894733333334</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2984,6 +3181,12 @@
         <v>0.9246657900000006</v>
       </c>
       <c r="U9" t="n">
+        <v>23.94991233333334</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3055,6 +3258,12 @@
         <v>0.9493236900000007</v>
       </c>
       <c r="U10" t="n">
+        <v>24.36087733333335</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3126,6 +3335,12 @@
         <v>0.973981590000001</v>
       </c>
       <c r="U11" t="n">
+        <v>24.77184233333335</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3197,6 +3412,12 @@
         <v>0.9986394900000012</v>
       </c>
       <c r="U12" t="n">
+        <v>25.18280733333335</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3268,6 +3489,12 @@
         <v>1.023297390000001</v>
       </c>
       <c r="U13" t="n">
+        <v>25.59377233333336</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3339,6 +3566,12 @@
         <v>1.051037512500002</v>
       </c>
       <c r="U14" t="n">
+        <v>29.44081141666669</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3410,6 +3643,12 @@
         <v>1.081859857500002</v>
       </c>
       <c r="U15" t="n">
+        <v>29.95451716666669</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3481,6 +3720,12 @@
         <v>1.112682202500001</v>
       </c>
       <c r="U16" t="n">
+        <v>30.46822291666669</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3552,6 +3797,12 @@
         <v>1.143504547500002</v>
       </c>
       <c r="U17" t="n">
+        <v>30.98192866666669</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3623,6 +3874,12 @@
         <v>1.174326892500001</v>
       </c>
       <c r="U18" t="n">
+        <v>31.49563441666669</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3694,6 +3951,12 @@
         <v>1.205149237500002</v>
       </c>
       <c r="U19" t="n">
+        <v>32.00934016666669</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3765,6 +4028,12 @@
         <v>1.235971582500002</v>
       </c>
       <c r="U20" t="n">
+        <v>32.5230459166667</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3836,6 +4105,12 @@
         <v>1.266793927500003</v>
       </c>
       <c r="U21" t="n">
+        <v>33.0367516666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3907,6 +4182,12 @@
         <v>1.297616272500003</v>
       </c>
       <c r="U22" t="n">
+        <v>33.55045741666671</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3978,6 +4259,12 @@
         <v>1.328438617500003</v>
       </c>
       <c r="U23" t="n">
+        <v>34.06416316666672</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4049,6 +4336,12 @@
         <v>1.359260962500004</v>
       </c>
       <c r="U24" t="n">
+        <v>34.57786891666672</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4120,6 +4413,12 @@
         <v>1.390083307500004</v>
       </c>
       <c r="U25" t="n">
+        <v>35.09157466666673</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4191,6 +4490,12 @@
         <v>1.415606307500004</v>
       </c>
       <c r="U26" t="n">
+        <v>39.59530225000007</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4262,6 +4567,12 @@
         <v>1.435829962500004</v>
       </c>
       <c r="U27" t="n">
+        <v>39.93236316666674</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4333,6 +4644,12 @@
         <v>1.456053617500004</v>
       </c>
       <c r="U28" t="n">
+        <v>40.2694240833334</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4404,6 +4721,12 @@
         <v>1.476277272500004</v>
       </c>
       <c r="U29" t="n">
+        <v>40.60648500000007</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4475,6 +4798,12 @@
         <v>1.496500927500004</v>
       </c>
       <c r="U30" t="n">
+        <v>40.94354591666674</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4546,6 +4875,12 @@
         <v>1.516724582500004</v>
       </c>
       <c r="U31" t="n">
+        <v>41.2806068333334</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4617,6 +4952,12 @@
         <v>1.553711264000004</v>
       </c>
       <c r="U32" t="n">
+        <v>42.17643530000007</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4688,6 +5029,12 @@
         <v>1.607460972000004</v>
       </c>
       <c r="U33" t="n">
+        <v>43.07226376666673</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4759,6 +5106,12 @@
         <v>1.661210680000003</v>
       </c>
       <c r="U34" t="n">
+        <v>43.96809223333339</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4830,6 +5183,12 @@
         <v>1.714960388000003</v>
       </c>
       <c r="U35" t="n">
+        <v>44.86392070000006</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4901,6 +5260,12 @@
         <v>1.768710096000003</v>
       </c>
       <c r="U36" t="n">
+        <v>45.75974916666672</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4972,6 +5337,12 @@
         <v>1.822459804000003</v>
       </c>
       <c r="U37" t="n">
+        <v>46.65557763333339</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5043,6 +5414,12 @@
         <v>1.777160016000003</v>
       </c>
       <c r="U38" t="n">
+        <v>52.37475623333339</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5114,6 +5491,12 @@
         <v>1.632810732000003</v>
       </c>
       <c r="U39" t="n">
+        <v>49.96893483333339</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5185,6 +5568,12 @@
         <v>1.488461448000004</v>
       </c>
       <c r="U40" t="n">
+        <v>47.5631134333334</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5256,6 +5645,12 @@
         <v>1.344112164000004</v>
       </c>
       <c r="U41" t="n">
+        <v>45.15729203333341</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5327,6 +5722,12 @@
         <v>1.199762880000004</v>
       </c>
       <c r="U42" t="n">
+        <v>42.75147063333341</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5398,6 +5799,12 @@
         <v>1.055413596000005</v>
       </c>
       <c r="U43" t="n">
+        <v>40.34564923333342</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5469,6 +5876,12 @@
         <v>0.9110643120000054</v>
       </c>
       <c r="U44" t="n">
+        <v>37.93982783333342</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5540,6 +5953,12 @@
         <v>0.7667150280000058</v>
       </c>
       <c r="U45" t="n">
+        <v>35.53400643333343</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5611,6 +6030,12 @@
         <v>0.6223657440000061</v>
       </c>
       <c r="U46" t="n">
+        <v>33.12818503333344</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5682,6 +6107,12 @@
         <v>0.4780164600000064</v>
       </c>
       <c r="U47" t="n">
+        <v>30.72236363333344</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5753,6 +6184,12 @@
         <v>0.3336671760000066</v>
       </c>
       <c r="U48" t="n">
+        <v>28.31654223333344</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5824,6 +6261,12 @@
         <v>0.1893178920000067</v>
       </c>
       <c r="U49" t="n">
+        <v>25.91072083333345</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5895,6 +6338,12 @@
         <v>0.05857162500000342</v>
       </c>
       <c r="U50" t="n">
+        <v>29.33823256666678</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5966,6 +6415,12 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6037,6 +6492,12 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6108,6 +6569,12 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6179,6 +6646,12 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6250,6 +6723,12 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6321,6 +6800,12 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6392,6 +6877,12 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6463,6 +6954,12 @@
         <v>0</v>
       </c>
       <c r="U58" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6534,6 +7031,12 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6605,6 +7108,12 @@
         <v>0</v>
       </c>
       <c r="U60" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6676,6 +7185,12 @@
         <v>0</v>
       </c>
       <c r="U61" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6747,6 +7262,12 @@
         <v>0</v>
       </c>
       <c r="U62" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6818,6 +7339,12 @@
         <v>0</v>
       </c>
       <c r="U63" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6889,6 +7416,12 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6960,6 +7493,12 @@
         <v>0</v>
       </c>
       <c r="U65" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7031,6 +7570,12 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7102,6 +7647,12 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7173,6 +7724,12 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7244,6 +7801,12 @@
         <v>0</v>
       </c>
       <c r="U69" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7315,6 +7878,12 @@
         <v>0</v>
       </c>
       <c r="U70" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7386,6 +7955,12 @@
         <v>0</v>
       </c>
       <c r="U71" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7457,6 +8032,12 @@
         <v>0</v>
       </c>
       <c r="U72" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7528,6 +8109,12 @@
         <v>0</v>
       </c>
       <c r="U73" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -10177,7 +10764,7 @@
         <v>51.38067</v>
       </c>
       <c r="F2" t="n">
-        <v>10.65214728000001</v>
+        <v>11.02201305000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -10186,13 +10773,13 @@
         <v>360</v>
       </c>
       <c r="I2" t="n">
-        <v>1218.16123728</v>
+        <v>1218.53110305</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1218.16123728</v>
+        <v>1218.53110305</v>
       </c>
       <c r="L2" t="n">
         <v>360</v>
@@ -10712,7 +11299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12538,7 +13125,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -12546,14 +13133,14 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>109.876</v>
+        <v>25.59377233333336</v>
       </c>
       <c r="G39" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -12570,7 +13157,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2035-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12587,7 +13174,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -12595,14 +13182,14 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>109.876</v>
       </c>
       <c r="G40" t="n">
-        <v>109.876</v>
+        <v>190</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -12636,7 +13223,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -12644,18 +13231,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>all_deliveries_ordered_within_lead_time</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>109.876</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41">
-        <f>=</f>
-        <v/>
+        <v>109.876</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="I41" t="b">
         <v>1</v>
@@ -12665,7 +13253,11 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12680,7 +13272,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SOURCE_NOT_AVAILABLE</t>
+          <t>LEAD_TIME_VIOLATED</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -12688,7 +13280,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>all_orders_from_available_sources</t>
+          <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -12724,27 +13316,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
+          <t>all_orders_from_available_sources</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>23.42490800000007</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>70</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <f>=</f>
+        <v/>
       </c>
       <c r="I43" t="b">
         <v>1</v>
@@ -12754,11 +13345,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>2036-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12773,7 +13360,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -12781,14 +13368,14 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>153.052</v>
+        <v>23.42490800000007</v>
       </c>
       <c r="G44" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -12805,7 +13392,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12822,7 +13409,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -12830,14 +13417,14 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>153.0518</v>
+        <v>35.09157466666673</v>
       </c>
       <c r="G45" t="n">
-        <v>153.052</v>
+        <v>70</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -12854,7 +13441,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12871,7 +13458,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -12879,170 +13466,170 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="G46" t="n">
+        <v>190</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>153.0518</v>
+      </c>
+      <c r="G47" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46">
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48">
         <f>=</f>
         <v/>
       </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D49" t="n">
         <v>2036</v>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47">
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49">
         <f>=</f>
         <v/>
       </c>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>25.44727350000007</v>
-      </c>
-      <c r="G48" t="n">
-        <v>70</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>2037-06, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>190</v>
-      </c>
-      <c r="G49" t="n">
-        <v>190</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -13057,7 +13644,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -13065,14 +13652,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>190</v>
+        <v>25.44727350000007</v>
       </c>
       <c r="G50" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -13089,7 +13676,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13106,7 +13693,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -13114,14 +13701,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>13.189</v>
+        <v>41.2806068333334</v>
       </c>
       <c r="G51" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -13138,7 +13725,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2037-06, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13155,7 +13742,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -13163,14 +13750,14 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>13.1882</v>
+        <v>190</v>
       </c>
       <c r="G52" t="n">
-        <v>13.189</v>
+        <v>190</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -13187,7 +13774,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -13204,7 +13791,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -13212,219 +13799,219 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>190</v>
+      </c>
+      <c r="G53" t="n">
+        <v>190</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="G54" t="n">
+        <v>130</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>13.1882</v>
+      </c>
+      <c r="G55" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53">
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56">
         <f>=</f>
         <v/>
       </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D57" t="n">
         <v>2037</v>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54">
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57">
         <f>=</f>
         <v/>
       </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>28.41642290000005</v>
-      </c>
-      <c r="G55" t="n">
-        <v>120</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I55" t="b">
-        <v>1</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>2038-01, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>190</v>
-      </c>
-      <c r="G56" t="n">
-        <v>190</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I56" t="b">
-        <v>1</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>190</v>
-      </c>
-      <c r="G57" t="n">
-        <v>190</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -13439,7 +14026,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -13447,14 +14034,14 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>71.77200000000001</v>
+        <v>28.41642290000005</v>
       </c>
       <c r="G58" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -13471,7 +14058,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2038-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13488,7 +14075,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -13496,14 +14083,14 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>71.7714</v>
+        <v>52.37475623333339</v>
       </c>
       <c r="G59" t="n">
-        <v>71.77200000000001</v>
+        <v>120</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -13520,7 +14107,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2038-01, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13537,7 +14124,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -13545,268 +14132,268 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>190</v>
+      </c>
+      <c r="G60" t="n">
+        <v>190</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>190</v>
+      </c>
+      <c r="G61" t="n">
+        <v>190</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>71.77200000000001</v>
+      </c>
+      <c r="G62" t="n">
+        <v>130</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>71.7714</v>
+      </c>
+      <c r="G63" t="n">
+        <v>71.77200000000001</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60">
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64">
         <f>=</f>
         <v/>
       </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D65" t="n">
         <v>2038</v>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61">
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65">
         <f>=</f>
         <v/>
       </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>120</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>2039-01, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>190</v>
-      </c>
-      <c r="G63" t="n">
-        <v>190</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>190</v>
-      </c>
-      <c r="G64" t="n">
-        <v>190</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>12.622</v>
-      </c>
-      <c r="G65" t="n">
-        <v>110</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -13821,7 +14408,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -13829,14 +14416,14 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>12.6216</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>12.622</v>
+        <v>120</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -13853,7 +14440,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2039-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13870,7 +14457,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -13878,14 +14465,14 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>130</v>
+        <v>29.33823256666678</v>
       </c>
       <c r="G67" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -13902,7 +14489,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2039-01, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13919,7 +14506,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -13927,14 +14514,14 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="G68" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -13951,7 +14538,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -13968,7 +14555,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -13976,317 +14563,317 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>190</v>
+      </c>
+      <c r="G69" t="n">
+        <v>190</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>12.622</v>
+      </c>
+      <c r="G70" t="n">
+        <v>110</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>12.6216</v>
+      </c>
+      <c r="G71" t="n">
+        <v>12.622</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>130</v>
+      </c>
+      <c r="G72" t="n">
+        <v>130</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>130</v>
+      </c>
+      <c r="G73" t="n">
+        <v>130</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69">
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74">
         <f>=</f>
         <v/>
       </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
+      <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D75" t="n">
         <v>2039</v>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70">
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75">
         <f>=</f>
         <v/>
       </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>120</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>2040-01, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>190</v>
-      </c>
-      <c r="G72" t="n">
-        <v>190</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>190</v>
-      </c>
-      <c r="G73" t="n">
-        <v>190</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I73" t="b">
-        <v>1</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>74.73699999999999</v>
-      </c>
-      <c r="G74" t="n">
-        <v>110</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I74" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>ordered_B_t</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>74.73690000000001</v>
-      </c>
-      <c r="G75" t="n">
-        <v>74.73699999999999</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -14301,7 +14888,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -14309,14 +14896,14 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -14333,7 +14920,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2040-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14350,7 +14937,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -14358,14 +14945,14 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>130</v>
+        <v>32.50000476666667</v>
       </c>
       <c r="G77" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -14382,7 +14969,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2040-01, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14399,7 +14986,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -14407,72 +14994,366 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>190</v>
+      </c>
+      <c r="G78" t="n">
+        <v>190</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>190</v>
+      </c>
+      <c r="G79" t="n">
+        <v>190</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>74.73699999999999</v>
+      </c>
+      <c r="G80" t="n">
+        <v>110</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>74.73690000000001</v>
+      </c>
+      <c r="G81" t="n">
+        <v>74.73699999999999</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>130</v>
+      </c>
+      <c r="G82" t="n">
+        <v>130</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>130</v>
+      </c>
+      <c r="G83" t="n">
+        <v>130</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F78" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78">
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84">
         <f>=</f>
         <v/>
       </c>
-      <c r="I78" t="b">
-        <v>1</v>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
+      <c r="K84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D85" t="n">
         <v>2040</v>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79">
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85">
         <f>=</f>
         <v/>
       </c>
-      <c r="I79" t="b">
-        <v>1</v>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23211,7 +24092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23253,7 +24134,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11517.764487147</v>
+        <v>11518.134352917</v>
       </c>
     </row>
     <row r="3">
@@ -23273,7 +24154,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9142.897763133344</v>
+        <v>9143.267628903344</v>
       </c>
     </row>
     <row r="4">
@@ -23413,7 +24294,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8.009111996264416</v>
+        <v>8.009369189956718</v>
       </c>
     </row>
     <row r="11">
@@ -23433,7 +24314,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.357700076003974</v>
+        <v>6.357957269696277</v>
       </c>
     </row>
     <row r="12">
@@ -23593,7 +24474,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>56.08181714700014</v>
+        <v>56.45168291700014</v>
       </c>
     </row>
     <row r="20">
@@ -23709,11 +24590,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>prep_holding_mln</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>0.36986577</v>
       </c>
     </row>
     <row r="26">
@@ -23729,11 +24610,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>prep_holding_months</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -23749,11 +24630,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -23769,11 +24650,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>0</v>
+          <t>guideline_violations</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -23789,11 +24670,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>checks_total</t>
+          <t>warnings</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -23809,11 +24690,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>73</v>
+      <c r="D32" t="n">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
